--- a/data/employees/EMP091/AST-EMP091-06.xlsx
+++ b/data/employees/EMP091/AST-EMP091-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Resource Utilization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System Resource Utilization - Alex Garcia (IT)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Alex Garcia | Role: Lead | Location: Fremont | Date: 2025-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>79</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CPU %</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Memory %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Disk %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Network (Mbps)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROD-APP-01</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>67</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55</v>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>86</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Automation backlog refinement. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PROD-SQL-02</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C6" t="n">
-        <v>81</v>
-      </c>
-      <c r="D6" t="n">
-        <v>88</v>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>880</v>
+        <v>71</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>Section 1: Customer escalation analysis. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEV-WEB-01</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>40</v>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>69</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEST-API-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D8" t="n">
-        <v>62</v>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>450</v>
+        <v>74</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Operational risk review. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>91</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>68</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>89</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>81</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>86</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>73</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>91</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>71</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>92</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>66</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>78</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>92</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>82</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp091 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>89</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP091</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP091 contributes to ast emp091 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>